--- a/research/traditional_assets/database/data/nigeria/nigeria_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05384</v>
+        <v>0.139</v>
       </c>
       <c r="E2">
-        <v>0.07490000000000001</v>
+        <v>-0.0219</v>
       </c>
       <c r="G2">
-        <v>0.1614173228346457</v>
+        <v>0.04812268640930725</v>
       </c>
       <c r="H2">
-        <v>0.1614173228346457</v>
+        <v>0.04812268640930725</v>
       </c>
       <c r="I2">
-        <v>0.137289088863892</v>
+        <v>0.09254362771020624</v>
       </c>
       <c r="J2">
-        <v>0.136930329310688</v>
+        <v>0.08372994888066279</v>
       </c>
       <c r="K2">
-        <v>29.65</v>
+        <v>19.8</v>
       </c>
       <c r="L2">
-        <v>0.1667604049493813</v>
+        <v>0.1047065044949762</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.03506224066390041</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.08535353535353535</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03506224066390041</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.08535353535353535</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>50.05</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="V2">
-        <v>0.6941747572815534</v>
+        <v>1.336099585062241</v>
       </c>
       <c r="W2">
-        <v>-0.2987223899308821</v>
+        <v>0.2265446224256293</v>
       </c>
       <c r="X2">
-        <v>0.110052012580171</v>
+        <v>0.1763017646808936</v>
       </c>
       <c r="Y2">
-        <v>-0.4087744025110531</v>
+        <v>0.05024285774473569</v>
       </c>
       <c r="Z2">
-        <v>-8.775913129318855</v>
+        <v>4.918075422626788</v>
       </c>
       <c r="AA2">
-        <v>-0.2635376804724602</v>
+        <v>0.411790203727785</v>
       </c>
       <c r="AB2">
-        <v>0.1093861116045758</v>
+        <v>0.1763017646808936</v>
       </c>
       <c r="AC2">
-        <v>-0.3729237920770361</v>
+        <v>0.2354884390468914</v>
       </c>
       <c r="AD2">
-        <v>0.242</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.242</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-49.808</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.003345221309889138</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.00310886154004265</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-2.234344159339674</v>
+        <v>3.975308641975308</v>
       </c>
       <c r="AK2">
-        <v>-1.792170408750719</v>
+        <v>-1.824362606232295</v>
       </c>
       <c r="AL2">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.009128630705394191</v>
-      </c>
-      <c r="AO2">
-        <v>271.2222222222222</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.878838174273859</v>
-      </c>
-      <c r="AQ2">
-        <v>271.2222222222222</v>
+        <v>-3.389473684210527</v>
       </c>
     </row>
     <row r="3">
@@ -719,76 +716,79 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.113</v>
+        <v>0.139</v>
       </c>
       <c r="E3">
-        <v>0.07490000000000001</v>
+        <v>-0.0219</v>
       </c>
       <c r="G3">
-        <v>0.1168332052267487</v>
+        <v>0.04812268640930725</v>
       </c>
       <c r="H3">
-        <v>0.1168332052267487</v>
+        <v>0.04812268640930725</v>
       </c>
       <c r="I3">
-        <v>0.01083781706379708</v>
+        <v>0.09254362771020624</v>
       </c>
       <c r="J3">
-        <v>0.01083781706379708</v>
+        <v>0.08372994888066279</v>
       </c>
       <c r="K3">
-        <v>5.55</v>
+        <v>19.8</v>
       </c>
       <c r="L3">
-        <v>0.04265949269792468</v>
+        <v>0.1047065044949762</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.69</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03506224066390041</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.08535353535353535</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03506224066390041</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.08535353535353535</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>47</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.7568438003220612</v>
+        <v>1.336099585062241</v>
       </c>
       <c r="W3">
-        <v>0.06646706586826347</v>
+        <v>0.2265446224256293</v>
       </c>
       <c r="X3">
-        <v>0.1092545237638909</v>
+        <v>0.1763017646808936</v>
       </c>
       <c r="Y3">
-        <v>-0.04278745789562739</v>
+        <v>0.05024285774473569</v>
       </c>
       <c r="Z3">
-        <v>7.498559077809799</v>
+        <v>4.918075422626788</v>
       </c>
       <c r="AA3">
-        <v>0.08126801152737753</v>
+        <v>0.411790203727785</v>
       </c>
       <c r="AB3">
-        <v>0.1092545237638909</v>
+        <v>0.1763017646808936</v>
       </c>
       <c r="AC3">
-        <v>-0.02798651223651333</v>
+        <v>0.2354884390468914</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-47</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-3.112582781456954</v>
+        <v>3.975308641975308</v>
       </c>
       <c r="AK3">
-        <v>-1.140776699029126</v>
+        <v>-1.824362606232295</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,135 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-15.61461794019934</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>African Alliance Insurance Plc (NGSE:AFRINSURE)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.00532</v>
-      </c>
-      <c r="G4">
-        <v>0.2830188679245283</v>
-      </c>
-      <c r="H4">
-        <v>0.2830188679245283</v>
-      </c>
-      <c r="I4">
-        <v>0.4821802935010482</v>
-      </c>
-      <c r="J4">
-        <v>0.4796602565761661</v>
-      </c>
-      <c r="K4">
-        <v>24.1</v>
-      </c>
-      <c r="L4">
-        <v>0.5052410901467506</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>3.05</v>
-      </c>
-      <c r="V4">
-        <v>0.305</v>
-      </c>
-      <c r="W4">
-        <v>-0.6639118457300276</v>
-      </c>
-      <c r="X4">
-        <v>0.1108495013964512</v>
-      </c>
-      <c r="Y4">
-        <v>-0.7747613471264788</v>
-      </c>
-      <c r="Z4">
-        <v>-1.268279712842329</v>
-      </c>
-      <c r="AA4">
-        <v>-0.608343372472298</v>
-      </c>
-      <c r="AB4">
-        <v>0.1095176994452608</v>
-      </c>
-      <c r="AC4">
-        <v>-0.7178610719175588</v>
-      </c>
-      <c r="AD4">
-        <v>0.242</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.242</v>
-      </c>
-      <c r="AG4">
-        <v>-2.808</v>
-      </c>
-      <c r="AH4">
-        <v>0.0236281976176528</v>
-      </c>
-      <c r="AI4">
-        <v>-0.02336358370341765</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.3904338153503893</v>
-      </c>
-      <c r="AK4">
-        <v>0.2094272076372315</v>
-      </c>
-      <c r="AL4">
-        <v>0.09</v>
-      </c>
-      <c r="AM4">
-        <v>0.09</v>
-      </c>
-      <c r="AN4">
-        <v>0.01029787234042553</v>
-      </c>
-      <c r="AO4">
-        <v>255.5555555555556</v>
-      </c>
-      <c r="AP4">
-        <v>-0.1194893617021276</v>
-      </c>
-      <c r="AQ4">
-        <v>255.5555555555556</v>
+        <v>-3.389473684210527</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.139</v>
+        <v>0.183</v>
       </c>
       <c r="E2">
-        <v>-0.0219</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G2">
-        <v>0.04812268640930725</v>
+        <v>0.1089696071163825</v>
       </c>
       <c r="H2">
-        <v>0.04812268640930725</v>
+        <v>0.1089696071163825</v>
       </c>
       <c r="I2">
-        <v>0.09254362771020624</v>
+        <v>0.111934766493699</v>
       </c>
       <c r="J2">
-        <v>0.08372994888066279</v>
+        <v>0.1031279980885749</v>
       </c>
       <c r="K2">
-        <v>19.8</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>0.1047065044949762</v>
+        <v>0.08154188287620459</v>
       </c>
       <c r="M2">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="N2">
-        <v>0.03506224066390041</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="O2">
-        <v>0.08535353535353535</v>
+        <v>0.1281818181818182</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
-        <v>0.03506224066390041</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="R2">
-        <v>0.08535353535353535</v>
+        <v>0.1281818181818182</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>64.40000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="V2">
-        <v>1.336099585062241</v>
+        <v>0.7750759878419453</v>
       </c>
       <c r="W2">
-        <v>0.2265446224256293</v>
+        <v>0.1112234580384226</v>
       </c>
       <c r="X2">
-        <v>0.1763017646808936</v>
+        <v>0.1599773748412334</v>
       </c>
       <c r="Y2">
-        <v>0.05024285774473569</v>
+        <v>-0.04875391680281076</v>
       </c>
       <c r="Z2">
-        <v>4.918075422626788</v>
+        <v>4.131699846860643</v>
       </c>
       <c r="AA2">
-        <v>0.411790203727785</v>
+        <v>0.4260939339096098</v>
       </c>
       <c r="AB2">
-        <v>0.1763017646808936</v>
+        <v>0.1599773748412334</v>
       </c>
       <c r="AC2">
-        <v>0.2354884390468914</v>
+        <v>0.2661165590683764</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-64.40000000000001</v>
+        <v>-25.5</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,22 +681,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>3.975308641975308</v>
+        <v>-3.445945945945946</v>
       </c>
       <c r="AK2">
-        <v>-1.824362606232295</v>
+        <v>-0.8225806451612904</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>2.363067292644757</v>
+      </c>
       <c r="AP2">
-        <v>-3.389473684210527</v>
+        <v>-1.574074074074074</v>
+      </c>
+      <c r="AQ2">
+        <v>2.363067292644757</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.139</v>
+        <v>0.183</v>
       </c>
       <c r="E3">
-        <v>-0.0219</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G3">
-        <v>0.04812268640930725</v>
+        <v>0.1089696071163825</v>
       </c>
       <c r="H3">
-        <v>0.04812268640930725</v>
+        <v>0.1089696071163825</v>
       </c>
       <c r="I3">
-        <v>0.09254362771020624</v>
+        <v>0.111934766493699</v>
       </c>
       <c r="J3">
-        <v>0.08372994888066279</v>
+        <v>0.1031279980885749</v>
       </c>
       <c r="K3">
-        <v>19.8</v>
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>0.1047065044949762</v>
+        <v>0.08154188287620459</v>
       </c>
       <c r="M3">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="N3">
-        <v>0.03506224066390041</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="O3">
-        <v>0.08535353535353535</v>
+        <v>0.1281818181818182</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="Q3">
-        <v>0.03506224066390041</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="R3">
-        <v>0.08535353535353535</v>
+        <v>0.1281818181818182</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>64.40000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="V3">
-        <v>1.336099585062241</v>
+        <v>0.7750759878419453</v>
       </c>
       <c r="W3">
-        <v>0.2265446224256293</v>
+        <v>0.1112234580384226</v>
       </c>
       <c r="X3">
-        <v>0.1763017646808936</v>
+        <v>0.1599773748412334</v>
       </c>
       <c r="Y3">
-        <v>0.05024285774473569</v>
+        <v>-0.04875391680281076</v>
       </c>
       <c r="Z3">
-        <v>4.918075422626788</v>
+        <v>4.131699846860643</v>
       </c>
       <c r="AA3">
-        <v>0.411790203727785</v>
+        <v>0.4260939339096098</v>
       </c>
       <c r="AB3">
-        <v>0.1763017646808936</v>
+        <v>0.1599773748412334</v>
       </c>
       <c r="AC3">
-        <v>0.2354884390468914</v>
+        <v>0.2661165590683764</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-64.40000000000001</v>
+        <v>-25.5</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,22 +815,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>3.975308641975308</v>
+        <v>-3.445945945945946</v>
       </c>
       <c r="AK3">
-        <v>-1.824362606232295</v>
+        <v>-0.8225806451612904</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>2.363067292644757</v>
+      </c>
       <c r="AP3">
-        <v>-3.389473684210527</v>
+        <v>-1.574074074074074</v>
+      </c>
+      <c r="AQ3">
+        <v>2.363067292644757</v>
       </c>
     </row>
   </sheetData>
